--- a/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Configs/GameConfig/Datas/projectile.xlsx
@@ -49,16 +49,13 @@
     <t>move_ability</t>
   </si>
   <si>
-    <t>tracking_ability</t>
-  </si>
-  <si>
     <t>damage_ability</t>
   </si>
   <si>
     <t>lifetime</t>
   </si>
   <si>
-    <t>lst_ability</t>
+    <t>lst_ability#format=lite</t>
   </si>
   <si>
     <t>##type</t>
@@ -76,10 +73,13 @@
     <t>移动速度</t>
   </si>
   <si>
-    <t>追踪类型，旋转速度</t>
-  </si>
-  <si>
-    <t>穿透次数</t>
+    <t>是否根据速度计算伤害/穿透次数</t>
+  </si>
+  <si>
+    <t>生存时间</t>
+  </si>
+  <si>
+    <t>能力</t>
   </si>
   <si>
     <t>arrow</t>
@@ -91,10 +91,10 @@
     <t>30</t>
   </si>
   <si>
-    <t>none,0</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>true,1</t>
+  </si>
+  <si>
+    <t>{no_track,1000}</t>
   </si>
   <si>
     <t>fire_ball</t>
@@ -103,7 +103,7 @@
     <t>火球</t>
   </si>
   <si>
-    <t>1</t>
+    <t>true,0</t>
   </si>
 </sst>
 </file>
@@ -284,7 +284,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,6 +311,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -496,7 +514,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -509,73 +527,6 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -710,7 +661,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -722,219 +673,180 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1248,21 +1160,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.5454545454545" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="12.8181818181818" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1818181818182" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.4545454545455" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.3636363636364" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.5454545454545" style="5" customWidth="1"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="11.5454545454545" style="4" customWidth="1"/>
+    <col min="3" max="4" width="9" style="4"/>
+    <col min="5" max="5" width="12.8181818181818" style="4" customWidth="1"/>
+    <col min="6" max="6" width="16.4545454545455" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.3636363636364" style="4" customWidth="1"/>
+    <col min="8" max="8" width="28.7272727272727" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15.2727272727273" style="4" customWidth="1"/>
+    <col min="10" max="21" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:21">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1272,20 +1184,31 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="10"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" s="1" customFormat="1" spans="1:21">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6"/>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -1294,155 +1217,199 @@
       <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:21">
+      <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="17" t="s">
+    <row r="4" s="3" customFormat="1" spans="1:21">
+      <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+    <row r="5" spans="1:21">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="20">
+        <v>5</v>
+      </c>
+      <c r="H5" s="20" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,I5:O5),"}")</f>
+        <v>{{no_track,1000}}</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1">
+    <row r="6" spans="1:21">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="20">
+        <v>5</v>
+      </c>
+      <c r="H6" s="20" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,I6:O6),"}")</f>
+        <v>{{no_track,1000}}</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4">
         <v>0</v>
       </c>
-      <c r="D5" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="29" t="s">
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="31" t="s">
+      <c r="F7" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="20">
+        <v>5</v>
+      </c>
+      <c r="H7" s="20" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,I7:O7),"}")</f>
+        <v>{{no_track,1000}}</v>
+      </c>
+      <c r="I7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="32">
+    </row>
+    <row r="8" spans="1:21">
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="20">
         <v>5</v>
       </c>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="31" t="s">
+      <c r="H8" s="20" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,I8:O8),"}")</f>
+        <v>{{no_track,1000}}</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>21</v>
-      </c>
-      <c r="H6" s="32">
-        <v>5</v>
-      </c>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="32">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="H4:I4"/>
+  <mergeCells count="1">
+    <mergeCell ref="C1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Configs/GameConfig/Datas/projectile.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -73,7 +73,7 @@
     <t>移动速度</t>
   </si>
   <si>
-    <t>是否根据速度计算伤害/穿透次数</t>
+    <t>是否根据速度计算伤害,速度伤害倍率，穿透次数</t>
   </si>
   <si>
     <t>生存时间</t>
@@ -91,7 +91,7 @@
     <t>30</t>
   </si>
   <si>
-    <t>true,1</t>
+    <t>true,0.05,1</t>
   </si>
   <si>
     <t>{no_track,1000}</t>
@@ -101,9 +101,6 @@
   </si>
   <si>
     <t>火球</t>
-  </si>
-  <si>
-    <t>true,0</t>
   </si>
 </sst>
 </file>
@@ -284,30 +281,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -661,7 +640,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -685,16 +664,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="7">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
@@ -703,85 +682,85 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -804,40 +783,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1167,7 +1146,7 @@
     <col min="2" max="2" width="11.5454545454545" style="4" customWidth="1"/>
     <col min="3" max="4" width="9" style="4"/>
     <col min="5" max="5" width="12.8181818181818" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.4545454545455" style="4" customWidth="1"/>
+    <col min="6" max="6" width="51.1818181818182" style="4" customWidth="1"/>
     <col min="7" max="7" width="10.3636363636364" style="4" customWidth="1"/>
     <col min="8" max="8" width="28.7272727272727" style="4" customWidth="1"/>
     <col min="9" max="9" width="15.2727272727273" style="4" customWidth="1"/>
@@ -1370,7 +1349,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G7" s="20">
         <v>5</v>
@@ -1394,7 +1373,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G8" s="20">
         <v>5</v>

--- a/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Configs/GameConfig/Datas/projectile.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -55,6 +55,9 @@
     <t>lifetime</t>
   </si>
   <si>
+    <t>tracking</t>
+  </si>
+  <si>
     <t>lst_ability#format=lite</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>生存时间</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>能力</t>
   </si>
   <si>
@@ -94,7 +100,7 @@
     <t>true,0.05,1</t>
   </si>
   <si>
-    <t>{no_track,1000}</t>
+    <t>no_track,1000</t>
   </si>
   <si>
     <t>fire_ball</t>
@@ -281,7 +287,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,6 +314,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -493,7 +517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -505,6 +529,43 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -640,7 +701,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -652,119 +713,119 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -780,19 +841,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -804,6 +883,15 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -813,19 +901,25 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1139,256 +1233,268 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="9" style="4"/>
+    <col min="1" max="1" width="9" style="4" customWidth="1"/>
     <col min="2" max="2" width="11.5454545454545" style="4" customWidth="1"/>
-    <col min="3" max="4" width="9" style="4"/>
+    <col min="3" max="4" width="9" style="4" customWidth="1"/>
     <col min="5" max="5" width="12.8181818181818" style="4" customWidth="1"/>
-    <col min="6" max="6" width="51.1818181818182" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.3636363636364" style="4" customWidth="1"/>
-    <col min="8" max="8" width="28.7272727272727" style="4" customWidth="1"/>
-    <col min="9" max="9" width="15.2727272727273" style="4" customWidth="1"/>
-    <col min="10" max="21" width="9" style="5"/>
+    <col min="6" max="6" width="51.1818181818182" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.3636363636364" style="6" customWidth="1"/>
+    <col min="8" max="8" width="18.9090909090909" style="6" customWidth="1"/>
+    <col min="9" max="9" width="28.7272727272727" style="4" customWidth="1"/>
+    <col min="10" max="10" width="18.9090909090909" style="7" customWidth="1"/>
+    <col min="11" max="21" width="9" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:21">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:22">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:21">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:22">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
+      <c r="I2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:21">
-      <c r="A3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="11" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:22">
+      <c r="A3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
+      <c r="D3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:21">
-      <c r="A4" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15" t="s">
+    <row r="4" s="3" customFormat="1" spans="1:22">
+      <c r="A4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="F4" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="G4" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
+      <c r="H4" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="28"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
-        <v>17</v>
+    <row r="5" spans="1:22">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30" t="s">
+        <v>19</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="20">
+      <c r="E5" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="6">
         <v>5</v>
       </c>
-      <c r="H5" s="20" t="str">
-        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,I5:O5),"}")</f>
-        <v>{{no_track,1000}}</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>21</v>
+      <c r="H5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="4" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,J5:O5),"}")</f>
+        <v>{}</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
+    <row r="6" spans="1:22">
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
       <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="19" t="s">
+      <c r="D6" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="20">
+      <c r="E6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6">
         <v>5</v>
       </c>
-      <c r="H6" s="20" t="str">
-        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,I6:O6),"}")</f>
-        <v>{{no_track,1000}}</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>21</v>
-      </c>
+      <c r="H6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="4" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,J6:O6),"}")</f>
+        <v>{}</v>
+      </c>
+      <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:22">
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4">
         <v>0</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="6">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="20">
-        <v>5</v>
-      </c>
-      <c r="H7" s="20" t="str">
-        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,I7:O7),"}")</f>
-        <v>{{no_track,1000}}</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>21</v>
-      </c>
+      <c r="I7" s="4" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,J7:O7),"}")</f>
+        <v>{}</v>
+      </c>
+      <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:22">
       <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6">
+        <v>5</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="20">
-        <v>5</v>
-      </c>
-      <c r="H8" s="20" t="str">
-        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,I8:O8),"}")</f>
-        <v>{{no_track,1000}}</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>21</v>
-      </c>
+      <c r="I8" s="4" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,J8:O8),"}")</f>
+        <v>{}</v>
+      </c>
+      <c r="J8" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Configs/GameConfig/Datas/projectile.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -76,7 +76,22 @@
     <t>移动速度</t>
   </si>
   <si>
-    <t>是否根据速度计算伤害,速度伤害倍率，穿透次数</t>
+    <t>是否根据速度计算伤害</t>
+  </si>
+  <si>
+    <t>伤害速度倍率</t>
+  </si>
+  <si>
+    <t>穿透次数</t>
+  </si>
+  <si>
+    <t>存活时间</t>
+  </si>
+  <si>
+    <t>追踪类型</t>
+  </si>
+  <si>
+    <t>能力（预留了4个位置)</t>
   </si>
   <si>
     <t>生存时间</t>
@@ -97,7 +112,13 @@
     <t>30</t>
   </si>
   <si>
-    <t>true,0.05,1</t>
+    <t>true</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>no_track,1000</t>
@@ -555,7 +576,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -566,9 +589,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -825,7 +846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -841,10 +862,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -853,43 +883,70 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -898,28 +955,37 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1233,268 +1299,414 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
     <col min="2" max="2" width="11.5454545454545" style="4" customWidth="1"/>
-    <col min="3" max="4" width="9" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12.8181818181818" style="4" customWidth="1"/>
-    <col min="6" max="6" width="51.1818181818182" style="5" customWidth="1"/>
-    <col min="7" max="7" width="10.3636363636364" style="6" customWidth="1"/>
-    <col min="8" max="8" width="18.9090909090909" style="6" customWidth="1"/>
-    <col min="9" max="9" width="28.7272727272727" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.9090909090909" style="7" customWidth="1"/>
-    <col min="11" max="21" width="9" style="7" customWidth="1"/>
+    <col min="3" max="4" width="9" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.90909090909091" style="5" customWidth="1"/>
+    <col min="6" max="6" width="24.0909090909091" style="5" customWidth="1"/>
+    <col min="7" max="7" width="24.0909090909091" style="6" customWidth="1"/>
+    <col min="8" max="9" width="14.6363636363636" style="7" customWidth="1"/>
+    <col min="10" max="10" width="16.4545454545455" style="7" customWidth="1"/>
+    <col min="11" max="13" width="16.4545454545455" style="8" customWidth="1"/>
+    <col min="14" max="14" width="14.6363636363636" style="8" customWidth="1"/>
+    <col min="15" max="15" width="15.2727272727273" style="9" customWidth="1"/>
+    <col min="16" max="16" width="17.7272727272727" style="6" customWidth="1"/>
+    <col min="17" max="17" width="10.3636363636364" style="7" customWidth="1"/>
+    <col min="18" max="18" width="18.9090909090909" style="7" customWidth="1"/>
+    <col min="19" max="19" width="28.7272727272727" style="5" customWidth="1"/>
+    <col min="20" max="20" width="18.9090909090909" style="10" customWidth="1"/>
+    <col min="21" max="31" width="9" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:22">
-      <c r="A1" s="8" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:32">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:22">
-      <c r="A2" s="8" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:32">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="P2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="Q2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="R2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="S2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:22">
-      <c r="A3" s="16" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:32">
+      <c r="A3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
+      <c r="B3" s="24"/>
+      <c r="C3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="34"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="34"/>
+      <c r="Z3" s="34"/>
+      <c r="AA3" s="34"/>
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="34"/>
+      <c r="AD3" s="34"/>
+      <c r="AE3" s="34"/>
+      <c r="AF3" s="34"/>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:22">
-      <c r="A4" s="23" t="s">
+    <row r="4" s="3" customFormat="1" spans="1:32">
+      <c r="A4" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="28"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
+      <c r="J4" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="44"/>
+      <c r="U4" s="45"/>
+      <c r="V4" s="45"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="45"/>
+      <c r="Y4" s="45"/>
+      <c r="Z4" s="45"/>
+      <c r="AA4" s="45"/>
+      <c r="AB4" s="45"/>
+      <c r="AC4" s="45"/>
+      <c r="AD4" s="45"/>
+      <c r="AE4" s="45"/>
+      <c r="AF4" s="45"/>
     </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="4">
+    <row r="5" spans="1:32">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5">
         <v>0</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="D5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="7">
         <v>5</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="4" t="str">
-        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,J5:O5),"}")</f>
+      <c r="J5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="9" t="str">
+        <f>_xlfn.CONCAT(0,",",E5)</f>
+        <v>0,30</v>
+      </c>
+      <c r="P5" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,"0",F5:H5)</f>
+        <v>0,true,0.05,1</v>
+      </c>
+      <c r="Q5" s="7" t="str">
+        <f>_xlfn.CONCAT("0",",",I5)</f>
+        <v>0,5</v>
+      </c>
+      <c r="R5" s="7" t="str">
+        <f>J5</f>
+        <v>no_track,1000</v>
+      </c>
+      <c r="S5" s="5" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,K5:N5),"}")</f>
         <v>{}</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="4">
+    <row r="6" spans="1:32">
+      <c r="A6" s="46"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="7">
         <v>5</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="4" t="str">
-        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,J6:O6),"}")</f>
+      <c r="J6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="9" t="str">
+        <f>_xlfn.CONCAT(0,",",E6)</f>
+        <v>0,30</v>
+      </c>
+      <c r="P6" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,"0",F6:H6)</f>
+        <v>0,true,0.05,1</v>
+      </c>
+      <c r="Q6" s="7" t="str">
+        <f>_xlfn.CONCAT("0",",",I6)</f>
+        <v>0,5</v>
+      </c>
+      <c r="R6" s="7" t="str">
+        <f>J6</f>
+        <v>no_track,1000</v>
+      </c>
+      <c r="S6" s="5" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,K6:N6),"}")</f>
         <v>{}</v>
       </c>
-      <c r="J6" s="4"/>
+      <c r="T6" s="4"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:32">
       <c r="B7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="4">
+        <v>31</v>
+      </c>
+      <c r="C7" s="5">
         <v>0</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="D7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="7">
         <v>5</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="4" t="str">
-        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,J7:O7),"}")</f>
+      <c r="J7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="9" t="str">
+        <f>_xlfn.CONCAT(0,",",E7)</f>
+        <v>0,30</v>
+      </c>
+      <c r="P7" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,"0",F7:H7)</f>
+        <v>0,true,0.05,1</v>
+      </c>
+      <c r="Q7" s="7" t="str">
+        <f>_xlfn.CONCAT("0",",",I7)</f>
+        <v>0,5</v>
+      </c>
+      <c r="R7" s="7" t="str">
+        <f>J7</f>
+        <v>no_track,1000</v>
+      </c>
+      <c r="S7" s="5" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,K7:N7),"}")</f>
         <v>{}</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:22">
-      <c r="C8" s="4">
+    <row r="8" spans="1:32">
+      <c r="C8" s="5">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="D8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="7">
         <v>5</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="4" t="str">
-        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,J8:O8),"}")</f>
+      <c r="J8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="9" t="str">
+        <f>_xlfn.CONCAT(0,",",E8)</f>
+        <v>0,30</v>
+      </c>
+      <c r="P8" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,"0",F8:H8)</f>
+        <v>0,true,0.05,1</v>
+      </c>
+      <c r="Q8" s="7" t="str">
+        <f>_xlfn.CONCAT("0",",",I8)</f>
+        <v>0,5</v>
+      </c>
+      <c r="R8" s="7" t="str">
+        <f>J8</f>
+        <v>no_track,1000</v>
+      </c>
+      <c r="S8" s="5" t="str">
+        <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,K8:N8),"}")</f>
         <v>{}</v>
       </c>
-      <c r="J8" s="4"/>
+      <c r="T8" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C1:I1"/>
+  <mergeCells count="2">
+    <mergeCell ref="C1:S1"/>
+    <mergeCell ref="K4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Configs/GameConfig/Datas/projectile.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -118,10 +118,13 @@
     <t>0.05</t>
   </si>
   <si>
+    <t>no_track,1000</t>
+  </si>
+  <si>
+    <t>{knockback,0,10}</t>
+  </si>
+  <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>no_track,1000</t>
   </si>
   <si>
     <t>fire_ball</t>
@@ -308,30 +311,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -722,7 +707,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -746,16 +731,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="10">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
@@ -764,89 +749,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -866,12 +851,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -904,19 +883,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -931,19 +898,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -972,12 +930,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1308,208 +1260,208 @@
     <col min="5" max="5" width="9.90909090909091" style="5" customWidth="1"/>
     <col min="6" max="6" width="24.0909090909091" style="5" customWidth="1"/>
     <col min="7" max="7" width="24.0909090909091" style="6" customWidth="1"/>
-    <col min="8" max="9" width="14.6363636363636" style="7" customWidth="1"/>
-    <col min="10" max="10" width="16.4545454545455" style="7" customWidth="1"/>
-    <col min="11" max="13" width="16.4545454545455" style="8" customWidth="1"/>
-    <col min="14" max="14" width="14.6363636363636" style="8" customWidth="1"/>
-    <col min="15" max="15" width="15.2727272727273" style="9" customWidth="1"/>
+    <col min="8" max="9" width="14.6363636363636" style="5" customWidth="1"/>
+    <col min="10" max="10" width="16.4545454545455" style="5" customWidth="1"/>
+    <col min="11" max="13" width="16.4545454545455" style="7" customWidth="1"/>
+    <col min="14" max="14" width="14.6363636363636" style="7" customWidth="1"/>
+    <col min="15" max="15" width="15.2727272727273" style="7" customWidth="1"/>
     <col min="16" max="16" width="17.7272727272727" style="6" customWidth="1"/>
-    <col min="17" max="17" width="10.3636363636364" style="7" customWidth="1"/>
-    <col min="18" max="18" width="18.9090909090909" style="7" customWidth="1"/>
+    <col min="17" max="17" width="10.3636363636364" style="5" customWidth="1"/>
+    <col min="18" max="18" width="18.9090909090909" style="5" customWidth="1"/>
     <col min="19" max="19" width="28.7272727272727" style="5" customWidth="1"/>
-    <col min="20" max="20" width="18.9090909090909" style="10" customWidth="1"/>
-    <col min="21" max="31" width="9" style="10" customWidth="1"/>
+    <col min="20" max="20" width="18.9090909090909" style="8" customWidth="1"/>
+    <col min="21" max="31" width="9" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:32">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16"/>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:32">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="17" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="21" t="s">
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="Q2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="23" t="s">
+      <c r="R2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="S2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="11"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:32">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="34"/>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
     </row>
     <row r="4" s="3" customFormat="1" spans="1:32">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="38" t="s">
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="42" t="s">
+      <c r="R4" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="S4" s="43" t="s">
+      <c r="S4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="T4" s="44"/>
-      <c r="U4" s="45"/>
-      <c r="V4" s="45"/>
-      <c r="W4" s="45"/>
-      <c r="X4" s="45"/>
-      <c r="Y4" s="45"/>
-      <c r="Z4" s="45"/>
-      <c r="AA4" s="45"/>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="45"/>
-      <c r="AD4" s="45"/>
-      <c r="AE4" s="45"/>
-      <c r="AF4" s="45"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="34"/>
     </row>
     <row r="5" spans="1:32">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46" t="s">
+      <c r="A5" s="35"/>
+      <c r="B5" s="35" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="5">
@@ -1527,39 +1479,42 @@
       <c r="G5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="7">
-        <v>5</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="O5" s="9" t="str">
+      <c r="O5" s="7" t="str">
         <f>_xlfn.CONCAT(0,",",E5)</f>
         <v>0,30</v>
       </c>
       <c r="P5" s="6" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,"0",F5:H5)</f>
-        <v>0,true,0.05,1</v>
-      </c>
-      <c r="Q5" s="7" t="str">
+        <v>0,true,0.05,0</v>
+      </c>
+      <c r="Q5" s="5" t="str">
         <f>_xlfn.CONCAT("0",",",I5)</f>
         <v>0,5</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="5" t="str">
         <f>J5</f>
         <v>no_track,1000</v>
       </c>
       <c r="S5" s="5" t="str">
         <f>_xlfn.CONCAT("{",_xlfn.TEXTJOIN(",",TRUE,K5:N5),"}")</f>
-        <v>{}</v>
+        <v>{{knockback,0,10}}</v>
       </c>
     </row>
     <row r="6" spans="1:32">
-      <c r="A6" s="46"/>
-      <c r="B6" s="46"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="5">
         <v>1</v>
       </c>
@@ -1575,16 +1530,16 @@
       <c r="G6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="5">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="7">
-        <v>5</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" s="9" t="str">
+      <c r="O6" s="7" t="str">
         <f>_xlfn.CONCAT(0,",",E6)</f>
         <v>0,30</v>
       </c>
@@ -1592,11 +1547,11 @@
         <f>_xlfn.TEXTJOIN(",",TRUE,"0",F6:H6)</f>
         <v>0,true,0.05,1</v>
       </c>
-      <c r="Q6" s="7" t="str">
+      <c r="Q6" s="5" t="str">
         <f>_xlfn.CONCAT("0",",",I6)</f>
         <v>0,5</v>
       </c>
-      <c r="R6" s="7" t="str">
+      <c r="R6" s="5" t="str">
         <f>J6</f>
         <v>no_track,1000</v>
       </c>
@@ -1608,13 +1563,13 @@
     </row>
     <row r="7" spans="1:32">
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>26</v>
@@ -1625,16 +1580,16 @@
       <c r="G7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="7">
-        <v>5</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" s="9" t="str">
+      <c r="O7" s="7" t="str">
         <f>_xlfn.CONCAT(0,",",E7)</f>
         <v>0,30</v>
       </c>
@@ -1642,11 +1597,11 @@
         <f>_xlfn.TEXTJOIN(",",TRUE,"0",F7:H7)</f>
         <v>0,true,0.05,1</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="5" t="str">
         <f>_xlfn.CONCAT("0",",",I7)</f>
         <v>0,5</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="5" t="str">
         <f>J7</f>
         <v>no_track,1000</v>
       </c>
@@ -1661,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>26</v>
@@ -1672,16 +1627,16 @@
       <c r="G8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="5">
+        <v>5</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="7">
-        <v>5</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" s="9" t="str">
+      <c r="O8" s="7" t="str">
         <f>_xlfn.CONCAT(0,",",E8)</f>
         <v>0,30</v>
       </c>
@@ -1689,11 +1644,11 @@
         <f>_xlfn.TEXTJOIN(",",TRUE,"0",F8:H8)</f>
         <v>0,true,0.05,1</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="5" t="str">
         <f>_xlfn.CONCAT("0",",",I8)</f>
         <v>0,5</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="5" t="str">
         <f>J8</f>
         <v>no_track,1000</v>
       </c>
